--- a/ADD-ARTEFACT-XDM/ig/all-profiles.xlsx
+++ b/ADD-ARTEFACT-XDM/ig/all-profiles.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-03T13:57:35+00:00</t>
+    <t>2026-07-07T20:41:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ADD-ARTEFACT-XDM/ig/all-profiles.xlsx
+++ b/ADD-ARTEFACT-XDM/ig/all-profiles.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6362" uniqueCount="509">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6330" uniqueCount="508">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-07T20:41:51+00:00</t>
+    <t>2026-07-09T18:09:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -807,154 +807,158 @@
     <t>DocumentEntry.logicalId</t>
   </si>
   <si>
+    <t>Cette métadonnée représente un identifiant invariable pour toutes les versions de la fiche d'un document, à la différence de la métadonnée entryUUID qui a une valeur différente pour chaque version de la fiche</t>
+  </si>
+  <si>
+    <t>DocumentEntry.mimeType</t>
+  </si>
+  <si>
+    <t>Cette métadonnée représente le type de contenu du document, défini par le standard MIME.</t>
+  </si>
+  <si>
+    <t>DocumentEntry.availabilityStatus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cette métadonnée représente la pertinence de la version de la fiche d'un document. </t>
+  </si>
+  <si>
+    <t>**Availability Status**</t>
+  </si>
+  <si>
+    <t>https://mos.esante.gouv.fr/NOS/JDV_J52-AvailabilityStatus-CISIS/FHIR/JDV-J52-AvailabilityStatus-CISIS|20200424120000</t>
+  </si>
+  <si>
+    <t>DocumentEntry.hash</t>
+  </si>
+  <si>
+    <t>Cette métadonnée contient le résultat du hachage du document déposé</t>
+  </si>
+  <si>
+    <t>DocumentEntry.size</t>
+  </si>
+  <si>
+    <t xml:space="preserve">integer
+</t>
+  </si>
+  <si>
+    <t>Cette métadonnée correspond à la taille du document déposé.</t>
+  </si>
+  <si>
+    <t>DocumentEntry.languageCode</t>
+  </si>
+  <si>
+    <t>Cette métadonnée représente le code de la langue dans laquelle le document est rédigé.</t>
+  </si>
+  <si>
+    <t>Pour tous les documents produits système initiateur français : 'fr-FR'</t>
+  </si>
+  <si>
+    <t>DocumentEntry.author</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/fhir/pdlgc/StructureDefinition/AuthorDocumentEntry
+</t>
+  </si>
+  <si>
+    <t>Cette métadonnée représente les personnes physiques et/ou les systèmes (dispositifs, automates, services numériques référencés…) auteurs d’un document.</t>
+  </si>
+  <si>
+    <t>DocumentEntry.legalAuthenticator[x]</t>
+  </si>
+  <si>
+    <t>https://interop.esante.gouv.fr/ig/fhir/pdlgc/StructureDefinition/ActorPS
+https://interop.esante.gouv.fr/ig/fhir/pdlgc/StructureDefinition/ActorPatienthttps://interop.esante.gouv.fr/ig/fhir/pdlgc/StructureDefinition/ActorSystem</t>
+  </si>
+  <si>
+    <t>Cette métadonnée représente l'acteur prenant la responsabilité du contenu médical du document</t>
+  </si>
+  <si>
+    <t>XCN</t>
+  </si>
+  <si>
+    <t>DocumentEntry.repositoryUniqueId</t>
+  </si>
+  <si>
+    <t xml:space="preserve">oid
+</t>
+  </si>
+  <si>
+    <t>Cette métadonnée représente l'identifiant unique global de l'entrepôt de documents dans lequel est stocké le document</t>
+  </si>
+  <si>
+    <t>DocumentEntry.serviceStartTime</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dateTime
+</t>
+  </si>
+  <si>
+    <t>Cette métadonnée représente la date de début de l'acte de référence.</t>
+  </si>
+  <si>
+    <t>DocumentEntry.serviceStopTime</t>
+  </si>
+  <si>
+    <t>Cette métadonnée correspond à la date de fin de l'acte de référence, si connue.</t>
+  </si>
+  <si>
+    <t>DocumentEntry.sourcePatientID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/fhir/pdlgc/StructureDefinition/SourcePatientId
+</t>
+  </si>
+  <si>
+    <t>Cette métadonnée contient l'identifiant secondaire du patient dans le système d'information du producteur (IPP) ou l'INS, s'il n'y a pas d'identifiant secondaire.</t>
+  </si>
+  <si>
+    <t>DocumentEntry.sourcePatientInfo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/fhir/pdlgc/StructureDefinition/SourcePatientInfo
+</t>
+  </si>
+  <si>
+    <t>Cette métadonnée contient les traits d'identité du patient concerné par le document, connus par le producteur du document.</t>
+  </si>
+  <si>
+    <t>DocumentEntry.URI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">uri
+</t>
+  </si>
+  <si>
+    <t>Cette métadonnée n'est exploitée que par la transaction XDM 'Distribute document set on media ITI-32'</t>
+  </si>
+  <si>
+    <t>DocumentEntry.title</t>
+  </si>
+  <si>
+    <t>Cette métadonnée représente le titre du document.</t>
+  </si>
+  <si>
+    <t>DocumentEntry.comments</t>
+  </si>
+  <si>
+    <t>Cette métadonnée contient le commentaire associé au document.</t>
+  </si>
+  <si>
+    <t>DocumentEntry.patientID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/fhir/pdlgc/StructureDefinition/PatientId
+</t>
+  </si>
+  <si>
+    <t>Cette métadonnée représente l’identifiant du patient, en l’occurrence, le matricule INS (NIR ou NIA) du patient lorsque celui-ci est qualifié.</t>
+  </si>
+  <si>
+    <t>DocumentEntry.uniqueId</t>
+  </si>
+  <si>
     <t xml:space="preserve">Identifier
 </t>
-  </si>
-  <si>
-    <t>Cette métadonnée représente un identifiant invariable pour toutes les versions de la fiche d'un document, à la différence de la métadonnée entryUUID qui a une valeur différente pour chaque version de la fiche</t>
-  </si>
-  <si>
-    <t>DocumentEntry.mimeType</t>
-  </si>
-  <si>
-    <t>Cette métadonnée représente le type de contenu du document, défini par le standard MIME.</t>
-  </si>
-  <si>
-    <t>DocumentEntry.availabilityStatus</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cette métadonnée représente la pertinence de la version de la fiche d'un document. </t>
-  </si>
-  <si>
-    <t>**Availability Status**</t>
-  </si>
-  <si>
-    <t>https://mos.esante.gouv.fr/NOS/JDV_J52-AvailabilityStatus-CISIS/FHIR/JDV-J52-AvailabilityStatus-CISIS|20200424120000</t>
-  </si>
-  <si>
-    <t>DocumentEntry.hash</t>
-  </si>
-  <si>
-    <t>Cette métadonnée contient le résultat du hachage du document déposé</t>
-  </si>
-  <si>
-    <t>DocumentEntry.size</t>
-  </si>
-  <si>
-    <t xml:space="preserve">integer
-</t>
-  </si>
-  <si>
-    <t>Cette métadonnée correspond à la taille du document déposé.</t>
-  </si>
-  <si>
-    <t>DocumentEntry.languageCode</t>
-  </si>
-  <si>
-    <t>Cette métadonnée représente le code de la langue dans laquelle le document est rédigé.</t>
-  </si>
-  <si>
-    <t>Pour tous les documents produits système initiateur français : 'fr-FR'</t>
-  </si>
-  <si>
-    <t>DocumentEntry.author</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/fhir/pdlgc/StructureDefinition/AuthorDocumentEntry
-</t>
-  </si>
-  <si>
-    <t>Cette métadonnée représente les personnes physiques et/ou les systèmes (dispositifs, automates, services numériques référencés…) auteurs d’un document.</t>
-  </si>
-  <si>
-    <t>DocumentEntry.legalAuthenticator[x]</t>
-  </si>
-  <si>
-    <t>https://interop.esante.gouv.fr/ig/fhir/pdlgc/StructureDefinition/ActorPS
-https://interop.esante.gouv.fr/ig/fhir/pdlgc/StructureDefinition/ActorPatienthttps://interop.esante.gouv.fr/ig/fhir/pdlgc/StructureDefinition/ActorSystem</t>
-  </si>
-  <si>
-    <t>Cette métadonnée représente l'acteur prenant la responsabilité du contenu médical du document</t>
-  </si>
-  <si>
-    <t>XCN</t>
-  </si>
-  <si>
-    <t>DocumentEntry.repositoryUniqueId</t>
-  </si>
-  <si>
-    <t xml:space="preserve">oid
-</t>
-  </si>
-  <si>
-    <t>Cette métadonnée représente l'identifiant unique global de l'entrepôt de documents dans lequel est stocké le document</t>
-  </si>
-  <si>
-    <t>DocumentEntry.serviceStartTime</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dateTime
-</t>
-  </si>
-  <si>
-    <t>Cette métadonnée représente la date de début de l'acte de référence.</t>
-  </si>
-  <si>
-    <t>DocumentEntry.serviceEndTime</t>
-  </si>
-  <si>
-    <t>Cette métadonnée correspond à la date de fin de l'acte de référence, si connue.</t>
-  </si>
-  <si>
-    <t>DocumentEntry.sourcePatientID</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/fhir/pdlgc/StructureDefinition/SourcePatientId
-</t>
-  </si>
-  <si>
-    <t>Cette métadonnée contient l'identifiant secondaire du patient dans le système d'information du producteur (IPP) ou l'INS, s'il n'y a pas d'identifiant secondaire.</t>
-  </si>
-  <si>
-    <t>DocumentEntry.sourcePatientInfo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/fhir/pdlgc/StructureDefinition/SourcePatientInfo
-</t>
-  </si>
-  <si>
-    <t>Cette métadonnée contient les traits d'identité du patient concerné par le document, connus par le producteur du document.</t>
-  </si>
-  <si>
-    <t>DocumentEntry.URI</t>
-  </si>
-  <si>
-    <t>Cette métadonnée n'est exploitée que par la transaction XDM 'Distribute document set on media ITI-32'</t>
-  </si>
-  <si>
-    <t>DocumentEntry.title</t>
-  </si>
-  <si>
-    <t>Cette métadonnée représente le titre du document.</t>
-  </si>
-  <si>
-    <t>DocumentEntry.comments</t>
-  </si>
-  <si>
-    <t>Cette métadonnée contient le commentaire associé au document.</t>
-  </si>
-  <si>
-    <t>DocumentEntry.patientID</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/fhir/pdlgc/StructureDefinition/PatientId
-</t>
-  </si>
-  <si>
-    <t>Cette métadonnée représente l’identifiant du patient, en l’occurrence, le matricule INS (NIR ou NIA) du patient.</t>
-  </si>
-  <si>
-    <t>DocumentEntry.uniqueId</t>
   </si>
   <si>
     <t xml:space="preserve">Identifiant unique affecté au document par son créateur. </t>
@@ -1110,12 +1114,6 @@
   </si>
   <si>
     <t>https://mos.esante.gouv.fr/NOS/JDV_J197-XdsTypesIdentifiantsReferenceId-CISIS/FHIR/JDV-J197-XdsTypesIdentifiantsReferenceId-CISIS|20220624120000</t>
-  </si>
-  <si>
-    <t>DocumentEntry.version</t>
-  </si>
-  <si>
-    <t>Cette métadonnée représente le numéro de version de la fiche d’un document.</t>
   </si>
   <si>
     <t>EventCode</t>
@@ -3415,7 +3413,7 @@
         <v>2</v>
       </c>
       <c r="B212" t="s" s="2">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="213">
@@ -3423,7 +3421,7 @@
         <v>4</v>
       </c>
       <c r="B213" t="s" s="2">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="214">
@@ -3439,7 +3437,7 @@
         <v>8</v>
       </c>
       <c r="B215" t="s" s="2">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="216">
@@ -3447,7 +3445,7 @@
         <v>9</v>
       </c>
       <c r="B216" t="s" s="2">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="217">
@@ -3501,7 +3499,7 @@
         <v>22</v>
       </c>
       <c r="B223" t="s" s="2">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="224">
@@ -3537,7 +3535,7 @@
         <v>30</v>
       </c>
       <c r="B228" t="s" s="2">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="229">
@@ -3585,7 +3583,7 @@
         <v>4</v>
       </c>
       <c r="B234" t="s" s="2">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="235">
@@ -3663,7 +3661,7 @@
         <v>22</v>
       </c>
       <c r="B244" t="s" s="2">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="245">
@@ -3699,7 +3697,7 @@
         <v>30</v>
       </c>
       <c r="B249" t="s" s="2">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="250">
@@ -3739,7 +3737,7 @@
         <v>2</v>
       </c>
       <c r="B254" t="s" s="2">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="255">
@@ -3747,7 +3745,7 @@
         <v>4</v>
       </c>
       <c r="B255" t="s" s="2">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="256">
@@ -3763,7 +3761,7 @@
         <v>8</v>
       </c>
       <c r="B257" t="s" s="2">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="258">
@@ -3771,7 +3769,7 @@
         <v>9</v>
       </c>
       <c r="B258" t="s" s="2">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="259">
@@ -3825,7 +3823,7 @@
         <v>22</v>
       </c>
       <c r="B265" t="s" s="2">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
     <row r="266">
@@ -3853,7 +3851,7 @@
         <v>28</v>
       </c>
       <c r="B269" t="s" s="2">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="270">
@@ -3861,7 +3859,7 @@
         <v>30</v>
       </c>
       <c r="B270" t="s" s="2">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="271">
@@ -3869,7 +3867,7 @@
         <v>31</v>
       </c>
       <c r="B271" t="s" s="2">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="272">
@@ -3885,7 +3883,7 @@
         <v>35</v>
       </c>
       <c r="B273" t="s" s="2">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="274">
@@ -3901,7 +3899,7 @@
         <v>2</v>
       </c>
       <c r="B275" t="s" s="2">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="276">
@@ -3909,7 +3907,7 @@
         <v>4</v>
       </c>
       <c r="B276" t="s" s="2">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="277">
@@ -3925,7 +3923,7 @@
         <v>8</v>
       </c>
       <c r="B278" t="s" s="2">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="279">
@@ -3933,7 +3931,7 @@
         <v>9</v>
       </c>
       <c r="B279" t="s" s="2">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="280">
@@ -3987,7 +3985,7 @@
         <v>22</v>
       </c>
       <c r="B286" t="s" s="2">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="287">
@@ -4023,7 +4021,7 @@
         <v>30</v>
       </c>
       <c r="B291" t="s" s="2">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="292">
@@ -4063,7 +4061,7 @@
         <v>2</v>
       </c>
       <c r="B296" t="s" s="2">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="297">
@@ -4071,7 +4069,7 @@
         <v>4</v>
       </c>
       <c r="B297" t="s" s="2">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="298">
@@ -4087,7 +4085,7 @@
         <v>8</v>
       </c>
       <c r="B299" t="s" s="2">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="300">
@@ -4095,7 +4093,7 @@
         <v>9</v>
       </c>
       <c r="B300" t="s" s="2">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="301">
@@ -4149,7 +4147,7 @@
         <v>22</v>
       </c>
       <c r="B307" t="s" s="2">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="308">
@@ -4185,7 +4183,7 @@
         <v>30</v>
       </c>
       <c r="B312" t="s" s="2">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="313">
@@ -4225,7 +4223,7 @@
         <v>2</v>
       </c>
       <c r="B317" t="s" s="2">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
     <row r="318">
@@ -4233,7 +4231,7 @@
         <v>4</v>
       </c>
       <c r="B318" t="s" s="2">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="319">
@@ -4249,7 +4247,7 @@
         <v>8</v>
       </c>
       <c r="B320" t="s" s="2">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
     <row r="321">
@@ -4257,7 +4255,7 @@
         <v>9</v>
       </c>
       <c r="B321" t="s" s="2">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="322">
@@ -4311,7 +4309,7 @@
         <v>22</v>
       </c>
       <c r="B328" t="s" s="2">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="329">
@@ -4347,7 +4345,7 @@
         <v>30</v>
       </c>
       <c r="B333" t="s" s="2">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="334">
@@ -4387,7 +4385,7 @@
         <v>2</v>
       </c>
       <c r="B338" t="s" s="2">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="339">
@@ -4395,7 +4393,7 @@
         <v>4</v>
       </c>
       <c r="B339" t="s" s="2">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="340">
@@ -4411,7 +4409,7 @@
         <v>8</v>
       </c>
       <c r="B341" t="s" s="2">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="342">
@@ -4419,7 +4417,7 @@
         <v>9</v>
       </c>
       <c r="B342" t="s" s="2">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="343">
@@ -4473,7 +4471,7 @@
         <v>22</v>
       </c>
       <c r="B349" t="s" s="2">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="350">
@@ -4509,7 +4507,7 @@
         <v>30</v>
       </c>
       <c r="B354" t="s" s="2">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="355">
@@ -4549,7 +4547,7 @@
         <v>2</v>
       </c>
       <c r="B359" t="s" s="2">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="360">
@@ -4557,7 +4555,7 @@
         <v>4</v>
       </c>
       <c r="B360" t="s" s="2">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="361">
@@ -4573,7 +4571,7 @@
         <v>8</v>
       </c>
       <c r="B362" t="s" s="2">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="363">
@@ -4581,7 +4579,7 @@
         <v>9</v>
       </c>
       <c r="B363" t="s" s="2">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="364">
@@ -4635,7 +4633,7 @@
         <v>22</v>
       </c>
       <c r="B370" t="s" s="2">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="371">
@@ -4671,7 +4669,7 @@
         <v>30</v>
       </c>
       <c r="B375" t="s" s="2">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="376">
@@ -4711,7 +4709,7 @@
         <v>2</v>
       </c>
       <c r="B380" t="s" s="2">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="381">
@@ -4719,7 +4717,7 @@
         <v>4</v>
       </c>
       <c r="B381" t="s" s="2">
-        <v>418</v>
+        <v>417</v>
       </c>
     </row>
     <row r="382">
@@ -4735,7 +4733,7 @@
         <v>8</v>
       </c>
       <c r="B383" t="s" s="2">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="384">
@@ -4743,7 +4741,7 @@
         <v>9</v>
       </c>
       <c r="B384" t="s" s="2">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="385">
@@ -4797,7 +4795,7 @@
         <v>22</v>
       </c>
       <c r="B391" t="s" s="2">
-        <v>420</v>
+        <v>419</v>
       </c>
     </row>
     <row r="392">
@@ -4833,7 +4831,7 @@
         <v>30</v>
       </c>
       <c r="B396" t="s" s="2">
-        <v>418</v>
+        <v>417</v>
       </c>
     </row>
     <row r="397">
@@ -4873,7 +4871,7 @@
         <v>2</v>
       </c>
       <c r="B401" t="s" s="2">
-        <v>443</v>
+        <v>442</v>
       </c>
     </row>
     <row r="402">
@@ -4881,7 +4879,7 @@
         <v>4</v>
       </c>
       <c r="B402" t="s" s="2">
-        <v>444</v>
+        <v>443</v>
       </c>
     </row>
     <row r="403">
@@ -4897,7 +4895,7 @@
         <v>8</v>
       </c>
       <c r="B404" t="s" s="2">
-        <v>443</v>
+        <v>442</v>
       </c>
     </row>
     <row r="405">
@@ -4905,7 +4903,7 @@
         <v>9</v>
       </c>
       <c r="B405" t="s" s="2">
-        <v>443</v>
+        <v>442</v>
       </c>
     </row>
     <row r="406">
@@ -4959,7 +4957,7 @@
         <v>22</v>
       </c>
       <c r="B412" t="s" s="2">
-        <v>445</v>
+        <v>444</v>
       </c>
     </row>
     <row r="413">
@@ -4995,7 +4993,7 @@
         <v>30</v>
       </c>
       <c r="B417" t="s" s="2">
-        <v>444</v>
+        <v>443</v>
       </c>
     </row>
     <row r="418">
@@ -5035,7 +5033,7 @@
         <v>2</v>
       </c>
       <c r="B422" t="s" s="2">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="423">
@@ -5043,7 +5041,7 @@
         <v>4</v>
       </c>
       <c r="B423" t="s" s="2">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="424">
@@ -5059,7 +5057,7 @@
         <v>8</v>
       </c>
       <c r="B425" t="s" s="2">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="426">
@@ -5067,7 +5065,7 @@
         <v>9</v>
       </c>
       <c r="B426" t="s" s="2">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="427">
@@ -5121,7 +5119,7 @@
         <v>22</v>
       </c>
       <c r="B433" t="s" s="2">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="434">
@@ -5157,7 +5155,7 @@
         <v>30</v>
       </c>
       <c r="B438" t="s" s="2">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="439">
@@ -5197,7 +5195,7 @@
         <v>2</v>
       </c>
       <c r="B443" t="s" s="2">
-        <v>483</v>
+        <v>482</v>
       </c>
     </row>
     <row r="444">
@@ -5205,7 +5203,7 @@
         <v>4</v>
       </c>
       <c r="B444" t="s" s="2">
-        <v>484</v>
+        <v>483</v>
       </c>
     </row>
     <row r="445">
@@ -5221,7 +5219,7 @@
         <v>8</v>
       </c>
       <c r="B446" t="s" s="2">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="447">
@@ -5229,7 +5227,7 @@
         <v>9</v>
       </c>
       <c r="B447" t="s" s="2">
-        <v>486</v>
+        <v>485</v>
       </c>
     </row>
     <row r="448">
@@ -5283,7 +5281,7 @@
         <v>22</v>
       </c>
       <c r="B454" t="s" s="2">
-        <v>487</v>
+        <v>486</v>
       </c>
     </row>
     <row r="455">
@@ -5319,7 +5317,7 @@
         <v>30</v>
       </c>
       <c r="B459" t="s" s="2">
-        <v>484</v>
+        <v>483</v>
       </c>
     </row>
     <row r="460">
@@ -5359,7 +5357,7 @@
         <v>2</v>
       </c>
       <c r="B464" t="s" s="2">
-        <v>497</v>
+        <v>496</v>
       </c>
     </row>
     <row r="465">
@@ -5367,7 +5365,7 @@
         <v>4</v>
       </c>
       <c r="B465" t="s" s="2">
-        <v>498</v>
+        <v>497</v>
       </c>
     </row>
     <row r="466">
@@ -5383,7 +5381,7 @@
         <v>8</v>
       </c>
       <c r="B467" t="s" s="2">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="468">
@@ -5391,7 +5389,7 @@
         <v>9</v>
       </c>
       <c r="B468" t="s" s="2">
-        <v>500</v>
+        <v>499</v>
       </c>
     </row>
     <row r="469">
@@ -5445,7 +5443,7 @@
         <v>22</v>
       </c>
       <c r="B475" t="s" s="2">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="476">
@@ -5481,7 +5479,7 @@
         <v>30</v>
       </c>
       <c r="B480" t="s" s="2">
-        <v>498</v>
+        <v>497</v>
       </c>
     </row>
     <row r="481">
@@ -5515,7 +5513,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AK170"/>
+  <dimension ref="A1:AK169"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="18.51171875" customWidth="true" bestFit="true"/>
@@ -13824,13 +13822,13 @@
         <v>73</v>
       </c>
       <c r="L81" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="M81" t="s" s="2">
         <v>253</v>
       </c>
-      <c r="M81" t="s" s="2">
-        <v>254</v>
-      </c>
       <c r="N81" t="s" s="2">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="O81" s="2"/>
       <c r="P81" s="2"/>
@@ -13901,10 +13899,10 @@
         <v>244</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C82" t="s" s="2">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D82" s="2"/>
       <c r="E82" t="s" s="2">
@@ -13930,10 +13928,10 @@
         <v>89</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="O82" s="2"/>
       <c r="P82" s="2"/>
@@ -13984,7 +13982,7 @@
         <v>73</v>
       </c>
       <c r="AG82" t="s" s="2">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="AH82" t="s" s="2">
         <v>79</v>
@@ -14004,10 +14002,10 @@
         <v>244</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C83" t="s" s="2">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="D83" s="2"/>
       <c r="E83" t="s" s="2">
@@ -14033,10 +14031,10 @@
         <v>193</v>
       </c>
       <c r="M83" t="s" s="2">
+        <v>257</v>
+      </c>
+      <c r="N83" t="s" s="2">
         <v>258</v>
-      </c>
-      <c r="N83" t="s" s="2">
-        <v>259</v>
       </c>
       <c r="O83" s="2"/>
       <c r="P83" s="2"/>
@@ -14067,7 +14065,7 @@
       </c>
       <c r="Z83" s="2"/>
       <c r="AA83" t="s" s="2">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="AB83" t="s" s="2">
         <v>73</v>
@@ -14085,7 +14083,7 @@
         <v>73</v>
       </c>
       <c r="AG83" t="s" s="2">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="AH83" t="s" s="2">
         <v>79</v>
@@ -14105,10 +14103,10 @@
         <v>244</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C84" t="s" s="2">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D84" s="2"/>
       <c r="E84" t="s" s="2">
@@ -14134,10 +14132,10 @@
         <v>89</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="O84" s="2"/>
       <c r="P84" s="2"/>
@@ -14188,7 +14186,7 @@
         <v>73</v>
       </c>
       <c r="AG84" t="s" s="2">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="AH84" t="s" s="2">
         <v>79</v>
@@ -14208,10 +14206,10 @@
         <v>244</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C85" t="s" s="2">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D85" s="2"/>
       <c r="E85" t="s" s="2">
@@ -14234,13 +14232,13 @@
         <v>73</v>
       </c>
       <c r="L85" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="M85" t="s" s="2">
         <v>264</v>
       </c>
-      <c r="M85" t="s" s="2">
-        <v>265</v>
-      </c>
       <c r="N85" t="s" s="2">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="O85" s="2"/>
       <c r="P85" s="2"/>
@@ -14291,7 +14289,7 @@
         <v>73</v>
       </c>
       <c r="AG85" t="s" s="2">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="AH85" t="s" s="2">
         <v>79</v>
@@ -14311,10 +14309,10 @@
         <v>244</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C86" t="s" s="2">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D86" s="2"/>
       <c r="E86" t="s" s="2">
@@ -14340,10 +14338,10 @@
         <v>89</v>
       </c>
       <c r="M86" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="N86" t="s" s="2">
         <v>267</v>
-      </c>
-      <c r="N86" t="s" s="2">
-        <v>268</v>
       </c>
       <c r="O86" s="2"/>
       <c r="P86" s="2"/>
@@ -14394,7 +14392,7 @@
         <v>73</v>
       </c>
       <c r="AG86" t="s" s="2">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="AH86" t="s" s="2">
         <v>79</v>
@@ -14414,10 +14412,10 @@
         <v>244</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C87" t="s" s="2">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D87" s="2"/>
       <c r="E87" t="s" s="2">
@@ -14440,13 +14438,13 @@
         <v>73</v>
       </c>
       <c r="L87" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="M87" t="s" s="2">
         <v>270</v>
       </c>
-      <c r="M87" t="s" s="2">
-        <v>271</v>
-      </c>
       <c r="N87" t="s" s="2">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="O87" s="2"/>
       <c r="P87" s="2"/>
@@ -14497,7 +14495,7 @@
         <v>73</v>
       </c>
       <c r="AG87" t="s" s="2">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="AH87" t="s" s="2">
         <v>79</v>
@@ -14517,10 +14515,10 @@
         <v>244</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C88" t="s" s="2">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="D88" s="2"/>
       <c r="E88" t="s" s="2">
@@ -14543,13 +14541,13 @@
         <v>73</v>
       </c>
       <c r="L88" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="M88" t="s" s="2">
         <v>273</v>
       </c>
-      <c r="M88" t="s" s="2">
+      <c r="N88" t="s" s="2">
         <v>274</v>
-      </c>
-      <c r="N88" t="s" s="2">
-        <v>275</v>
       </c>
       <c r="O88" s="2"/>
       <c r="P88" s="2"/>
@@ -14600,7 +14598,7 @@
         <v>73</v>
       </c>
       <c r="AG88" t="s" s="2">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="AH88" t="s" s="2">
         <v>79</v>
@@ -14620,10 +14618,10 @@
         <v>244</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C89" t="s" s="2">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="D89" s="2"/>
       <c r="E89" t="s" s="2">
@@ -14646,13 +14644,13 @@
         <v>73</v>
       </c>
       <c r="L89" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="M89" t="s" s="2">
         <v>277</v>
       </c>
-      <c r="M89" t="s" s="2">
-        <v>278</v>
-      </c>
       <c r="N89" t="s" s="2">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="O89" s="2"/>
       <c r="P89" s="2"/>
@@ -14703,7 +14701,7 @@
         <v>73</v>
       </c>
       <c r="AG89" t="s" s="2">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="AH89" t="s" s="2">
         <v>79</v>
@@ -14723,10 +14721,10 @@
         <v>244</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C90" t="s" s="2">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="D90" s="2"/>
       <c r="E90" t="s" s="2">
@@ -14749,13 +14747,13 @@
         <v>73</v>
       </c>
       <c r="L90" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="M90" t="s" s="2">
         <v>280</v>
       </c>
-      <c r="M90" t="s" s="2">
-        <v>281</v>
-      </c>
       <c r="N90" t="s" s="2">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="O90" s="2"/>
       <c r="P90" s="2"/>
@@ -14806,7 +14804,7 @@
         <v>73</v>
       </c>
       <c r="AG90" t="s" s="2">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="AH90" t="s" s="2">
         <v>79</v>
@@ -14826,10 +14824,10 @@
         <v>244</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C91" t="s" s="2">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="D91" s="2"/>
       <c r="E91" t="s" s="2">
@@ -14852,13 +14850,13 @@
         <v>73</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="O91" s="2"/>
       <c r="P91" s="2"/>
@@ -14909,7 +14907,7 @@
         <v>73</v>
       </c>
       <c r="AG91" t="s" s="2">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="AH91" t="s" s="2">
         <v>74</v>
@@ -14929,10 +14927,10 @@
         <v>244</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C92" t="s" s="2">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="D92" s="2"/>
       <c r="E92" t="s" s="2">
@@ -14955,13 +14953,13 @@
         <v>73</v>
       </c>
       <c r="L92" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="M92" t="s" s="2">
         <v>285</v>
       </c>
-      <c r="M92" t="s" s="2">
-        <v>286</v>
-      </c>
       <c r="N92" t="s" s="2">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="O92" s="2"/>
       <c r="P92" s="2"/>
@@ -15012,7 +15010,7 @@
         <v>73</v>
       </c>
       <c r="AG92" t="s" s="2">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="AH92" t="s" s="2">
         <v>79</v>
@@ -15032,10 +15030,10 @@
         <v>244</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C93" t="s" s="2">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D93" s="2"/>
       <c r="E93" t="s" s="2">
@@ -15058,13 +15056,13 @@
         <v>73</v>
       </c>
       <c r="L93" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="M93" t="s" s="2">
         <v>288</v>
       </c>
-      <c r="M93" t="s" s="2">
-        <v>289</v>
-      </c>
       <c r="N93" t="s" s="2">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="O93" s="2"/>
       <c r="P93" s="2"/>
@@ -15115,7 +15113,7 @@
         <v>73</v>
       </c>
       <c r="AG93" t="s" s="2">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="AH93" t="s" s="2">
         <v>79</v>
@@ -15135,10 +15133,10 @@
         <v>244</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C94" t="s" s="2">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D94" s="2"/>
       <c r="E94" t="s" s="2">
@@ -15161,7 +15159,7 @@
         <v>73</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>89</v>
+        <v>290</v>
       </c>
       <c r="M94" t="s" s="2">
         <v>291</v>
@@ -15218,7 +15216,7 @@
         <v>73</v>
       </c>
       <c r="AG94" t="s" s="2">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="AH94" t="s" s="2">
         <v>79</v>
@@ -15573,13 +15571,13 @@
         <v>73</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>253</v>
+        <v>300</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="N98" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="O98" s="2"/>
       <c r="P98" s="2"/>
@@ -15650,10 +15648,10 @@
         <v>244</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C99" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="D99" s="2"/>
       <c r="E99" t="s" s="2">
@@ -15679,10 +15677,10 @@
         <v>193</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="O99" s="2"/>
       <c r="P99" s="2"/>
@@ -15713,7 +15711,7 @@
       </c>
       <c r="Z99" s="2"/>
       <c r="AA99" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AB99" t="s" s="2">
         <v>73</v>
@@ -15731,7 +15729,7 @@
         <v>73</v>
       </c>
       <c r="AG99" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="AH99" t="s" s="2">
         <v>79</v>
@@ -15751,10 +15749,10 @@
         <v>244</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C100" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="D100" s="2"/>
       <c r="E100" t="s" s="2">
@@ -15765,7 +15763,7 @@
         <v>79</v>
       </c>
       <c r="H100" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="I100" t="s" s="2">
         <v>73</v>
@@ -15780,10 +15778,10 @@
         <v>193</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="O100" s="2"/>
       <c r="P100" s="2"/>
@@ -15814,7 +15812,7 @@
       </c>
       <c r="Z100" s="2"/>
       <c r="AA100" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="AB100" t="s" s="2">
         <v>73</v>
@@ -15832,13 +15830,13 @@
         <v>73</v>
       </c>
       <c r="AG100" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AH100" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AI100" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AJ100" t="s" s="2">
         <v>73</v>
@@ -15852,10 +15850,10 @@
         <v>244</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C101" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="D101" s="2"/>
       <c r="E101" t="s" s="2">
@@ -15878,13 +15876,13 @@
         <v>73</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="O101" s="2"/>
       <c r="P101" s="2"/>
@@ -15935,7 +15933,7 @@
         <v>73</v>
       </c>
       <c r="AG101" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="AH101" t="s" s="2">
         <v>74</v>
@@ -15955,10 +15953,10 @@
         <v>244</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C102" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="D102" s="2"/>
       <c r="E102" t="s" s="2">
@@ -15984,10 +15982,10 @@
         <v>193</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="O102" s="2"/>
       <c r="P102" s="2"/>
@@ -16018,7 +16016,7 @@
       </c>
       <c r="Z102" s="2"/>
       <c r="AA102" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="AB102" t="s" s="2">
         <v>73</v>
@@ -16036,7 +16034,7 @@
         <v>73</v>
       </c>
       <c r="AG102" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="AH102" t="s" s="2">
         <v>79</v>
@@ -16056,10 +16054,10 @@
         <v>244</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C103" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="D103" s="2"/>
       <c r="E103" t="s" s="2">
@@ -16085,10 +16083,10 @@
         <v>193</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="N103" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="O103" s="2"/>
       <c r="P103" s="2"/>
@@ -16119,7 +16117,7 @@
       </c>
       <c r="Z103" s="2"/>
       <c r="AA103" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AB103" t="s" s="2">
         <v>73</v>
@@ -16137,7 +16135,7 @@
         <v>73</v>
       </c>
       <c r="AG103" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AH103" t="s" s="2">
         <v>79</v>
@@ -16157,10 +16155,10 @@
         <v>244</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C104" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="D104" s="2"/>
       <c r="E104" t="s" s="2">
@@ -16186,10 +16184,10 @@
         <v>193</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="N104" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="O104" s="2"/>
       <c r="P104" s="2"/>
@@ -16220,7 +16218,7 @@
       </c>
       <c r="Z104" s="2"/>
       <c r="AA104" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AB104" t="s" s="2">
         <v>73</v>
@@ -16238,7 +16236,7 @@
         <v>73</v>
       </c>
       <c r="AG104" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AH104" t="s" s="2">
         <v>79</v>
@@ -16258,10 +16256,10 @@
         <v>244</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C105" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="D105" s="2"/>
       <c r="E105" t="s" s="2">
@@ -16287,10 +16285,10 @@
         <v>193</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="O105" s="2"/>
       <c r="P105" s="2"/>
@@ -16321,7 +16319,7 @@
       </c>
       <c r="Z105" s="2"/>
       <c r="AA105" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AB105" t="s" s="2">
         <v>73</v>
@@ -16339,7 +16337,7 @@
         <v>73</v>
       </c>
       <c r="AG105" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AH105" t="s" s="2">
         <v>79</v>
@@ -16359,10 +16357,10 @@
         <v>244</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C106" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="D106" s="2"/>
       <c r="E106" t="s" s="2">
@@ -16388,10 +16386,10 @@
         <v>89</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="N106" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="O106" s="2"/>
       <c r="P106" s="2"/>
@@ -16442,7 +16440,7 @@
         <v>73</v>
       </c>
       <c r="AG106" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AH106" t="s" s="2">
         <v>74</v>
@@ -16462,10 +16460,10 @@
         <v>244</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C107" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="D107" s="2"/>
       <c r="E107" t="s" s="2">
@@ -16488,13 +16486,13 @@
         <v>73</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="N107" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="O107" s="2"/>
       <c r="P107" s="2"/>
@@ -16545,7 +16543,7 @@
         <v>73</v>
       </c>
       <c r="AG107" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AH107" t="s" s="2">
         <v>74</v>
@@ -16565,10 +16563,10 @@
         <v>244</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C108" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="D108" s="2"/>
       <c r="E108" t="s" s="2">
@@ -16591,13 +16589,13 @@
         <v>73</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="N108" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="O108" s="2"/>
       <c r="P108" s="2"/>
@@ -16648,7 +16646,7 @@
         <v>73</v>
       </c>
       <c r="AG108" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AH108" t="s" s="2">
         <v>79</v>
@@ -16668,10 +16666,10 @@
         <v>244</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C109" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="D109" s="2"/>
       <c r="E109" t="s" s="2">
@@ -16697,10 +16695,10 @@
         <v>98</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="N109" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="O109" s="2"/>
       <c r="P109" s="2"/>
@@ -16751,7 +16749,7 @@
         <v>73</v>
       </c>
       <c r="AG109" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AH109" t="s" s="2">
         <v>74</v>
@@ -16771,10 +16769,10 @@
         <v>244</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C110" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="D110" s="2"/>
       <c r="E110" t="s" s="2">
@@ -16797,13 +16795,13 @@
         <v>73</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="N110" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="O110" s="2"/>
       <c r="P110" s="2"/>
@@ -16854,7 +16852,7 @@
         <v>73</v>
       </c>
       <c r="AG110" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AH110" t="s" s="2">
         <v>79</v>
@@ -16874,10 +16872,10 @@
         <v>244</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C111" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="D111" s="2"/>
       <c r="E111" t="s" s="2">
@@ -16900,13 +16898,13 @@
         <v>73</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="N111" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="O111" s="2"/>
       <c r="P111" s="2"/>
@@ -16957,7 +16955,7 @@
         <v>73</v>
       </c>
       <c r="AG111" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AH111" t="s" s="2">
         <v>79</v>
@@ -16977,10 +16975,10 @@
         <v>244</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C112" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="D112" s="2"/>
       <c r="E112" t="s" s="2">
@@ -17040,25 +17038,25 @@
       </c>
       <c r="Z112" s="2"/>
       <c r="AA112" t="s" s="2">
+        <v>346</v>
+      </c>
+      <c r="AB112" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC112" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD112" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE112" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF112" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AG112" t="s" s="2">
         <v>345</v>
-      </c>
-      <c r="AB112" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC112" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD112" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE112" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF112" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AG112" t="s" s="2">
-        <v>344</v>
       </c>
       <c r="AH112" t="s" s="2">
         <v>79</v>
@@ -17075,13 +17073,13 @@
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>244</v>
+        <v>347</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C113" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="D113" s="2"/>
       <c r="E113" t="s" s="2">
@@ -17092,7 +17090,7 @@
         <v>74</v>
       </c>
       <c r="H113" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="I113" t="s" s="2">
         <v>73</v>
@@ -17104,13 +17102,13 @@
         <v>73</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>264</v>
+        <v>76</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="N113" t="s" s="2">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="O113" s="2"/>
       <c r="P113" s="2"/>
@@ -17161,13 +17159,13 @@
         <v>73</v>
       </c>
       <c r="AG113" t="s" s="2">
-        <v>346</v>
+        <v>77</v>
       </c>
       <c r="AH113" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI113" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AJ113" t="s" s="2">
         <v>73</v>
@@ -17178,13 +17176,13 @@
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="C114" t="s" s="2">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="D114" s="2"/>
       <c r="E114" t="s" s="2">
@@ -17192,10 +17190,10 @@
       </c>
       <c r="F114" s="2"/>
       <c r="G114" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="H114" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="I114" t="s" s="2">
         <v>73</v>
@@ -17207,13 +17205,13 @@
         <v>73</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>76</v>
+        <v>193</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="N114" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="O114" s="2"/>
       <c r="P114" s="2"/>
@@ -17264,13 +17262,13 @@
         <v>73</v>
       </c>
       <c r="AG114" t="s" s="2">
-        <v>77</v>
+        <v>351</v>
       </c>
       <c r="AH114" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="AI114" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AJ114" t="s" s="2">
         <v>73</v>
@@ -17281,13 +17279,13 @@
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>348</v>
+        <v>86</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>352</v>
+        <v>86</v>
       </c>
       <c r="C115" t="s" s="2">
-        <v>352</v>
+        <v>86</v>
       </c>
       <c r="D115" s="2"/>
       <c r="E115" t="s" s="2">
@@ -17295,10 +17293,10 @@
       </c>
       <c r="F115" s="2"/>
       <c r="G115" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="H115" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="I115" t="s" s="2">
         <v>73</v>
@@ -17310,13 +17308,13 @@
         <v>73</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>193</v>
+        <v>76</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>353</v>
+        <v>86</v>
       </c>
       <c r="N115" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="O115" s="2"/>
       <c r="P115" s="2"/>
@@ -17367,13 +17365,13 @@
         <v>73</v>
       </c>
       <c r="AG115" t="s" s="2">
-        <v>352</v>
+        <v>77</v>
       </c>
       <c r="AH115" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AI115" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AJ115" t="s" s="2">
         <v>73</v>
@@ -17387,10 +17385,10 @@
         <v>86</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C116" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D116" s="2"/>
       <c r="E116" t="s" s="2">
@@ -17398,10 +17396,10 @@
       </c>
       <c r="F116" s="2"/>
       <c r="G116" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="H116" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="I116" t="s" s="2">
         <v>73</v>
@@ -17413,13 +17411,13 @@
         <v>73</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>76</v>
+        <v>356</v>
       </c>
       <c r="M116" t="s" s="2">
         <v>86</v>
       </c>
       <c r="N116" t="s" s="2">
-        <v>356</v>
+        <v>86</v>
       </c>
       <c r="O116" s="2"/>
       <c r="P116" s="2"/>
@@ -17470,13 +17468,13 @@
         <v>73</v>
       </c>
       <c r="AG116" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="AH116" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="AI116" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AJ116" t="s" s="2">
         <v>73</v>
@@ -17487,13 +17485,13 @@
     </row>
     <row r="117">
       <c r="A117" t="s" s="2">
-        <v>86</v>
+        <v>357</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>87</v>
+        <v>361</v>
       </c>
       <c r="C117" t="s" s="2">
-        <v>87</v>
+        <v>361</v>
       </c>
       <c r="D117" s="2"/>
       <c r="E117" t="s" s="2">
@@ -17501,10 +17499,10 @@
       </c>
       <c r="F117" s="2"/>
       <c r="G117" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="H117" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="I117" t="s" s="2">
         <v>73</v>
@@ -17516,15 +17514,17 @@
         <v>73</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>357</v>
+        <v>76</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>86</v>
+        <v>364</v>
       </c>
       <c r="N117" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="O117" s="2"/>
+        <v>365</v>
+      </c>
+      <c r="O117" t="s" s="2">
+        <v>366</v>
+      </c>
       <c r="P117" s="2"/>
       <c r="Q117" t="s" s="2">
         <v>73</v>
@@ -17573,30 +17573,30 @@
         <v>73</v>
       </c>
       <c r="AG117" t="s" s="2">
-        <v>87</v>
+        <v>361</v>
       </c>
       <c r="AH117" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AI117" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AJ117" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AK117" t="s" s="2">
-        <v>73</v>
+        <v>367</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="s" s="2">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>362</v>
+        <v>368</v>
       </c>
       <c r="C118" t="s" s="2">
-        <v>362</v>
+        <v>368</v>
       </c>
       <c r="D118" s="2"/>
       <c r="E118" t="s" s="2">
@@ -17607,7 +17607,7 @@
         <v>74</v>
       </c>
       <c r="H118" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="I118" t="s" s="2">
         <v>73</v>
@@ -17619,17 +17619,15 @@
         <v>73</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="N118" t="s" s="2">
-        <v>366</v>
-      </c>
-      <c r="O118" t="s" s="2">
-        <v>367</v>
-      </c>
+        <v>370</v>
+      </c>
+      <c r="O118" s="2"/>
       <c r="P118" s="2"/>
       <c r="Q118" t="s" s="2">
         <v>73</v>
@@ -17678,41 +17676,41 @@
         <v>73</v>
       </c>
       <c r="AG118" t="s" s="2">
-        <v>362</v>
+        <v>371</v>
       </c>
       <c r="AH118" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI118" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AJ118" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AK118" t="s" s="2">
-        <v>368</v>
+        <v>73</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="C119" t="s" s="2">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="D119" s="2"/>
       <c r="E119" t="s" s="2">
-        <v>73</v>
+        <v>373</v>
       </c>
       <c r="F119" s="2"/>
       <c r="G119" t="s" s="2">
         <v>74</v>
       </c>
       <c r="H119" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="I119" t="s" s="2">
         <v>73</v>
@@ -17724,15 +17722,17 @@
         <v>73</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>89</v>
+        <v>374</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="N119" t="s" s="2">
-        <v>371</v>
-      </c>
-      <c r="O119" s="2"/>
+        <v>376</v>
+      </c>
+      <c r="O119" t="s" s="2">
+        <v>377</v>
+      </c>
       <c r="P119" s="2"/>
       <c r="Q119" t="s" s="2">
         <v>73</v>
@@ -17781,41 +17781,41 @@
         <v>73</v>
       </c>
       <c r="AG119" t="s" s="2">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="AH119" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI119" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AJ119" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AK119" t="s" s="2">
-        <v>73</v>
+        <v>379</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="s" s="2">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="C120" t="s" s="2">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="D120" s="2"/>
       <c r="E120" t="s" s="2">
-        <v>374</v>
+        <v>73</v>
       </c>
       <c r="F120" s="2"/>
       <c r="G120" t="s" s="2">
         <v>74</v>
       </c>
       <c r="H120" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="I120" t="s" s="2">
         <v>73</v>
@@ -17827,17 +17827,15 @@
         <v>73</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>375</v>
+        <v>89</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="N120" t="s" s="2">
-        <v>377</v>
-      </c>
-      <c r="O120" t="s" s="2">
-        <v>378</v>
-      </c>
+        <v>382</v>
+      </c>
+      <c r="O120" s="2"/>
       <c r="P120" s="2"/>
       <c r="Q120" t="s" s="2">
         <v>73</v>
@@ -17859,7 +17857,7 @@
         <v>73</v>
       </c>
       <c r="X120" t="s" s="2">
-        <v>73</v>
+        <v>383</v>
       </c>
       <c r="Y120" t="s" s="2">
         <v>73</v>
@@ -17886,30 +17884,30 @@
         <v>73</v>
       </c>
       <c r="AG120" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AH120" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI120" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AJ120" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AK120" t="s" s="2">
-        <v>380</v>
+        <v>73</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="s" s="2">
-        <v>358</v>
+        <v>384</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="C121" t="s" s="2">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="D121" s="2"/>
       <c r="E121" t="s" s="2">
@@ -17920,7 +17918,7 @@
         <v>74</v>
       </c>
       <c r="H121" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="I121" t="s" s="2">
         <v>73</v>
@@ -17932,13 +17930,13 @@
         <v>73</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>89</v>
+        <v>76</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="N121" t="s" s="2">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="O121" s="2"/>
       <c r="P121" s="2"/>
@@ -17962,7 +17960,7 @@
         <v>73</v>
       </c>
       <c r="X121" t="s" s="2">
-        <v>384</v>
+        <v>73</v>
       </c>
       <c r="Y121" t="s" s="2">
         <v>73</v>
@@ -17989,13 +17987,13 @@
         <v>73</v>
       </c>
       <c r="AG121" t="s" s="2">
-        <v>381</v>
+        <v>77</v>
       </c>
       <c r="AH121" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI121" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AJ121" t="s" s="2">
         <v>73</v>
@@ -18006,13 +18004,13 @@
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="C122" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="D122" s="2"/>
       <c r="E122" t="s" s="2">
@@ -18020,10 +18018,10 @@
       </c>
       <c r="F122" s="2"/>
       <c r="G122" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="H122" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="I122" t="s" s="2">
         <v>73</v>
@@ -18035,13 +18033,13 @@
         <v>73</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="N122" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="O122" s="2"/>
       <c r="P122" s="2"/>
@@ -18092,13 +18090,13 @@
         <v>73</v>
       </c>
       <c r="AG122" t="s" s="2">
-        <v>77</v>
+        <v>387</v>
       </c>
       <c r="AH122" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="AI122" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AJ122" t="s" s="2">
         <v>73</v>
@@ -18109,13 +18107,13 @@
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="C123" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="D123" s="2"/>
       <c r="E123" t="s" s="2">
@@ -18123,10 +18121,10 @@
       </c>
       <c r="F123" s="2"/>
       <c r="G123" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="H123" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="I123" t="s" s="2">
         <v>73</v>
@@ -18138,13 +18136,13 @@
         <v>73</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>89</v>
+        <v>76</v>
       </c>
       <c r="M123" t="s" s="2">
         <v>389</v>
       </c>
       <c r="N123" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="O123" s="2"/>
       <c r="P123" s="2"/>
@@ -18195,13 +18193,13 @@
         <v>73</v>
       </c>
       <c r="AG123" t="s" s="2">
-        <v>388</v>
+        <v>77</v>
       </c>
       <c r="AH123" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AI123" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AJ123" t="s" s="2">
         <v>73</v>
@@ -18212,13 +18210,13 @@
     </row>
     <row r="124">
       <c r="A124" t="s" s="2">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="C124" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="D124" s="2"/>
       <c r="E124" t="s" s="2">
@@ -18226,10 +18224,10 @@
       </c>
       <c r="F124" s="2"/>
       <c r="G124" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="H124" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="I124" t="s" s="2">
         <v>73</v>
@@ -18241,13 +18239,13 @@
         <v>73</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="N124" t="s" s="2">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="O124" s="2"/>
       <c r="P124" s="2"/>
@@ -18298,30 +18296,30 @@
         <v>73</v>
       </c>
       <c r="AG124" t="s" s="2">
-        <v>77</v>
+        <v>392</v>
       </c>
       <c r="AH124" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="AI124" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AJ124" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AK124" t="s" s="2">
-        <v>73</v>
+        <v>393</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C125" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="D125" s="2"/>
       <c r="E125" t="s" s="2">
@@ -18329,10 +18327,10 @@
       </c>
       <c r="F125" s="2"/>
       <c r="G125" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="H125" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="I125" t="s" s="2">
         <v>73</v>
@@ -18344,13 +18342,13 @@
         <v>73</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>89</v>
+        <v>76</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>390</v>
+        <v>396</v>
       </c>
       <c r="N125" t="s" s="2">
-        <v>390</v>
+        <v>397</v>
       </c>
       <c r="O125" s="2"/>
       <c r="P125" s="2"/>
@@ -18401,30 +18399,30 @@
         <v>73</v>
       </c>
       <c r="AG125" t="s" s="2">
-        <v>393</v>
+        <v>77</v>
       </c>
       <c r="AH125" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AI125" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AJ125" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AK125" t="s" s="2">
-        <v>394</v>
+        <v>73</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="s" s="2">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="C126" t="s" s="2">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="D126" s="2"/>
       <c r="E126" t="s" s="2">
@@ -18432,10 +18430,10 @@
       </c>
       <c r="F126" s="2"/>
       <c r="G126" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="H126" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="I126" t="s" s="2">
         <v>73</v>
@@ -18447,13 +18445,13 @@
         <v>73</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>76</v>
+        <v>300</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="N126" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="O126" s="2"/>
       <c r="P126" s="2"/>
@@ -18504,13 +18502,13 @@
         <v>73</v>
       </c>
       <c r="AG126" t="s" s="2">
-        <v>77</v>
+        <v>398</v>
       </c>
       <c r="AH126" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="AI126" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AJ126" t="s" s="2">
         <v>73</v>
@@ -18521,13 +18519,13 @@
     </row>
     <row r="127">
       <c r="A127" t="s" s="2">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C127" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="D127" s="2"/>
       <c r="E127" t="s" s="2">
@@ -18550,13 +18548,13 @@
         <v>73</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>253</v>
+        <v>89</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="N127" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="O127" s="2"/>
       <c r="P127" s="2"/>
@@ -18607,7 +18605,7 @@
         <v>73</v>
       </c>
       <c r="AG127" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AH127" t="s" s="2">
         <v>79</v>
@@ -18624,13 +18622,13 @@
     </row>
     <row r="128">
       <c r="A128" t="s" s="2">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="C128" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="D128" s="2"/>
       <c r="E128" t="s" s="2">
@@ -18656,10 +18654,10 @@
         <v>89</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="N128" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="O128" s="2"/>
       <c r="P128" s="2"/>
@@ -18710,7 +18708,7 @@
         <v>73</v>
       </c>
       <c r="AG128" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="AH128" t="s" s="2">
         <v>79</v>
@@ -18727,13 +18725,13 @@
     </row>
     <row r="129">
       <c r="A129" t="s" s="2">
-        <v>395</v>
+        <v>405</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="C129" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="D129" s="2"/>
       <c r="E129" t="s" s="2">
@@ -18741,10 +18739,10 @@
       </c>
       <c r="F129" s="2"/>
       <c r="G129" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="H129" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="I129" t="s" s="2">
         <v>73</v>
@@ -18756,13 +18754,13 @@
         <v>73</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>89</v>
+        <v>76</v>
       </c>
       <c r="M129" t="s" s="2">
         <v>405</v>
       </c>
       <c r="N129" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="O129" s="2"/>
       <c r="P129" s="2"/>
@@ -18813,13 +18811,13 @@
         <v>73</v>
       </c>
       <c r="AG129" t="s" s="2">
-        <v>404</v>
+        <v>77</v>
       </c>
       <c r="AH129" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AI129" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AJ129" t="s" s="2">
         <v>73</v>
@@ -18830,13 +18828,13 @@
     </row>
     <row r="130">
       <c r="A130" t="s" s="2">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="C130" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="D130" s="2"/>
       <c r="E130" t="s" s="2">
@@ -18844,10 +18842,10 @@
       </c>
       <c r="F130" s="2"/>
       <c r="G130" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="H130" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="I130" t="s" s="2">
         <v>73</v>
@@ -18859,13 +18857,13 @@
         <v>73</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="N130" t="s" s="2">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="O130" s="2"/>
       <c r="P130" s="2"/>
@@ -18916,13 +18914,13 @@
         <v>73</v>
       </c>
       <c r="AG130" t="s" s="2">
-        <v>77</v>
+        <v>408</v>
       </c>
       <c r="AH130" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="AI130" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AJ130" t="s" s="2">
         <v>73</v>
@@ -18933,7 +18931,7 @@
     </row>
     <row r="131">
       <c r="A131" t="s" s="2">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="B131" t="s" s="2">
         <v>409</v>
@@ -18947,10 +18945,10 @@
       </c>
       <c r="F131" s="2"/>
       <c r="G131" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="H131" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="I131" t="s" s="2">
         <v>73</v>
@@ -18962,13 +18960,13 @@
         <v>73</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>89</v>
+        <v>76</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="N131" t="s" s="2">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="O131" s="2"/>
       <c r="P131" s="2"/>
@@ -19019,13 +19017,13 @@
         <v>73</v>
       </c>
       <c r="AG131" t="s" s="2">
-        <v>409</v>
+        <v>77</v>
       </c>
       <c r="AH131" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AI131" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AJ131" t="s" s="2">
         <v>73</v>
@@ -19036,13 +19034,13 @@
     </row>
     <row r="132">
       <c r="A132" t="s" s="2">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="C132" t="s" s="2">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="D132" s="2"/>
       <c r="E132" t="s" s="2">
@@ -19050,10 +19048,10 @@
       </c>
       <c r="F132" s="2"/>
       <c r="G132" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="H132" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="I132" t="s" s="2">
         <v>73</v>
@@ -19065,13 +19063,13 @@
         <v>73</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>76</v>
+        <v>300</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>412</v>
+        <v>399</v>
       </c>
       <c r="N132" t="s" s="2">
-        <v>413</v>
+        <v>399</v>
       </c>
       <c r="O132" s="2"/>
       <c r="P132" s="2"/>
@@ -19122,13 +19120,13 @@
         <v>73</v>
       </c>
       <c r="AG132" t="s" s="2">
-        <v>77</v>
+        <v>413</v>
       </c>
       <c r="AH132" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="AI132" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AJ132" t="s" s="2">
         <v>73</v>
@@ -19139,7 +19137,7 @@
     </row>
     <row r="133">
       <c r="A133" t="s" s="2">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B133" t="s" s="2">
         <v>414</v>
@@ -19168,13 +19166,13 @@
         <v>73</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>253</v>
+        <v>89</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="N133" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="O133" s="2"/>
       <c r="P133" s="2"/>
@@ -19242,7 +19240,7 @@
     </row>
     <row r="134">
       <c r="A134" t="s" s="2">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B134" t="s" s="2">
         <v>415</v>
@@ -19274,10 +19272,10 @@
         <v>89</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="N134" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="O134" s="2"/>
       <c r="P134" s="2"/>
@@ -19345,7 +19343,7 @@
     </row>
     <row r="135">
       <c r="A135" t="s" s="2">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="B135" t="s" s="2">
         <v>416</v>
@@ -19359,10 +19357,10 @@
       </c>
       <c r="F135" s="2"/>
       <c r="G135" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="H135" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="I135" t="s" s="2">
         <v>73</v>
@@ -19374,13 +19372,13 @@
         <v>73</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>89</v>
+        <v>76</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>405</v>
+        <v>418</v>
       </c>
       <c r="N135" t="s" s="2">
-        <v>405</v>
+        <v>419</v>
       </c>
       <c r="O135" s="2"/>
       <c r="P135" s="2"/>
@@ -19431,13 +19429,13 @@
         <v>73</v>
       </c>
       <c r="AG135" t="s" s="2">
-        <v>416</v>
+        <v>77</v>
       </c>
       <c r="AH135" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AI135" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AJ135" t="s" s="2">
         <v>73</v>
@@ -19448,13 +19446,13 @@
     </row>
     <row r="136">
       <c r="A136" t="s" s="2">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="C136" t="s" s="2">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="D136" s="2"/>
       <c r="E136" t="s" s="2">
@@ -19465,7 +19463,7 @@
         <v>74</v>
       </c>
       <c r="H136" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="I136" t="s" s="2">
         <v>73</v>
@@ -19477,13 +19475,13 @@
         <v>73</v>
       </c>
       <c r="L136" t="s" s="2">
-        <v>76</v>
+        <v>300</v>
       </c>
       <c r="M136" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="N136" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="O136" s="2"/>
       <c r="P136" s="2"/>
@@ -19534,13 +19532,13 @@
         <v>73</v>
       </c>
       <c r="AG136" t="s" s="2">
-        <v>77</v>
+        <v>420</v>
       </c>
       <c r="AH136" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI136" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AJ136" t="s" s="2">
         <v>73</v>
@@ -19551,13 +19549,13 @@
     </row>
     <row r="137">
       <c r="A137" t="s" s="2">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="C137" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="D137" s="2"/>
       <c r="E137" t="s" s="2">
@@ -19565,10 +19563,10 @@
       </c>
       <c r="F137" s="2"/>
       <c r="G137" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="H137" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="I137" t="s" s="2">
         <v>73</v>
@@ -19580,13 +19578,13 @@
         <v>73</v>
       </c>
       <c r="L137" t="s" s="2">
-        <v>253</v>
+        <v>89</v>
       </c>
       <c r="M137" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="N137" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="O137" s="2"/>
       <c r="P137" s="2"/>
@@ -19637,13 +19635,13 @@
         <v>73</v>
       </c>
       <c r="AG137" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AH137" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="AI137" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AJ137" t="s" s="2">
         <v>73</v>
@@ -19654,13 +19652,13 @@
     </row>
     <row r="138">
       <c r="A138" t="s" s="2">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C138" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="D138" s="2"/>
       <c r="E138" t="s" s="2">
@@ -19668,10 +19666,10 @@
       </c>
       <c r="F138" s="2"/>
       <c r="G138" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="H138" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="I138" t="s" s="2">
         <v>73</v>
@@ -19686,10 +19684,10 @@
         <v>89</v>
       </c>
       <c r="M138" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="N138" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="O138" s="2"/>
       <c r="P138" s="2"/>
@@ -19740,13 +19738,13 @@
         <v>73</v>
       </c>
       <c r="AG138" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AH138" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AI138" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AJ138" t="s" s="2">
         <v>73</v>
@@ -19757,13 +19755,13 @@
     </row>
     <row r="139">
       <c r="A139" t="s" s="2">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="C139" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="D139" s="2"/>
       <c r="E139" t="s" s="2">
@@ -19789,10 +19787,10 @@
         <v>89</v>
       </c>
       <c r="M139" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="N139" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="O139" s="2"/>
       <c r="P139" s="2"/>
@@ -19843,7 +19841,7 @@
         <v>73</v>
       </c>
       <c r="AG139" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AH139" t="s" s="2">
         <v>74</v>
@@ -19860,13 +19858,13 @@
     </row>
     <row r="140">
       <c r="A140" t="s" s="2">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C140" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="D140" s="2"/>
       <c r="E140" t="s" s="2">
@@ -19892,10 +19890,10 @@
         <v>89</v>
       </c>
       <c r="M140" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="N140" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="O140" s="2"/>
       <c r="P140" s="2"/>
@@ -19946,7 +19944,7 @@
         <v>73</v>
       </c>
       <c r="AG140" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AH140" t="s" s="2">
         <v>74</v>
@@ -19963,13 +19961,13 @@
     </row>
     <row r="141">
       <c r="A141" t="s" s="2">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C141" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="D141" s="2"/>
       <c r="E141" t="s" s="2">
@@ -19995,10 +19993,10 @@
         <v>89</v>
       </c>
       <c r="M141" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="N141" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="O141" s="2"/>
       <c r="P141" s="2"/>
@@ -20049,7 +20047,7 @@
         <v>73</v>
       </c>
       <c r="AG141" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AH141" t="s" s="2">
         <v>74</v>
@@ -20066,13 +20064,13 @@
     </row>
     <row r="142">
       <c r="A142" t="s" s="2">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="C142" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="D142" s="2"/>
       <c r="E142" t="s" s="2">
@@ -20098,10 +20096,10 @@
         <v>89</v>
       </c>
       <c r="M142" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="N142" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="O142" s="2"/>
       <c r="P142" s="2"/>
@@ -20152,7 +20150,7 @@
         <v>73</v>
       </c>
       <c r="AG142" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AH142" t="s" s="2">
         <v>74</v>
@@ -20169,13 +20167,13 @@
     </row>
     <row r="143">
       <c r="A143" t="s" s="2">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C143" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="D143" s="2"/>
       <c r="E143" t="s" s="2">
@@ -20201,10 +20199,10 @@
         <v>89</v>
       </c>
       <c r="M143" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="N143" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="O143" s="2"/>
       <c r="P143" s="2"/>
@@ -20255,7 +20253,7 @@
         <v>73</v>
       </c>
       <c r="AG143" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AH143" t="s" s="2">
         <v>74</v>
@@ -20272,13 +20270,13 @@
     </row>
     <row r="144">
       <c r="A144" t="s" s="2">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="C144" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="D144" s="2"/>
       <c r="E144" t="s" s="2">
@@ -20304,10 +20302,10 @@
         <v>89</v>
       </c>
       <c r="M144" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="N144" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="O144" s="2"/>
       <c r="P144" s="2"/>
@@ -20358,7 +20356,7 @@
         <v>73</v>
       </c>
       <c r="AG144" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="AH144" t="s" s="2">
         <v>74</v>
@@ -20375,13 +20373,13 @@
     </row>
     <row r="145">
       <c r="A145" t="s" s="2">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C145" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="D145" s="2"/>
       <c r="E145" t="s" s="2">
@@ -20407,10 +20405,10 @@
         <v>89</v>
       </c>
       <c r="M145" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="N145" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="O145" s="2"/>
       <c r="P145" s="2"/>
@@ -20461,7 +20459,7 @@
         <v>73</v>
       </c>
       <c r="AG145" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AH145" t="s" s="2">
         <v>74</v>
@@ -20478,13 +20476,13 @@
     </row>
     <row r="146">
       <c r="A146" t="s" s="2">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C146" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="D146" s="2"/>
       <c r="E146" t="s" s="2">
@@ -20510,10 +20508,10 @@
         <v>89</v>
       </c>
       <c r="M146" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="N146" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="O146" s="2"/>
       <c r="P146" s="2"/>
@@ -20564,7 +20562,7 @@
         <v>73</v>
       </c>
       <c r="AG146" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="AH146" t="s" s="2">
         <v>74</v>
@@ -20581,13 +20579,13 @@
     </row>
     <row r="147">
       <c r="A147" t="s" s="2">
-        <v>417</v>
+        <v>442</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="C147" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="D147" s="2"/>
       <c r="E147" t="s" s="2">
@@ -20598,7 +20596,7 @@
         <v>74</v>
       </c>
       <c r="H147" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="I147" t="s" s="2">
         <v>73</v>
@@ -20610,13 +20608,13 @@
         <v>73</v>
       </c>
       <c r="L147" t="s" s="2">
-        <v>89</v>
+        <v>76</v>
       </c>
       <c r="M147" t="s" s="2">
         <v>442</v>
       </c>
       <c r="N147" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="O147" s="2"/>
       <c r="P147" s="2"/>
@@ -20667,13 +20665,13 @@
         <v>73</v>
       </c>
       <c r="AG147" t="s" s="2">
-        <v>441</v>
+        <v>77</v>
       </c>
       <c r="AH147" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI147" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AJ147" t="s" s="2">
         <v>73</v>
@@ -20684,13 +20682,13 @@
     </row>
     <row r="148">
       <c r="A148" t="s" s="2">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="C148" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="D148" s="2"/>
       <c r="E148" t="s" s="2">
@@ -20698,10 +20696,10 @@
       </c>
       <c r="F148" s="2"/>
       <c r="G148" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="H148" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="I148" t="s" s="2">
         <v>73</v>
@@ -20713,13 +20711,13 @@
         <v>73</v>
       </c>
       <c r="L148" t="s" s="2">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="M148" t="s" s="2">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="N148" t="s" s="2">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="O148" s="2"/>
       <c r="P148" s="2"/>
@@ -20770,13 +20768,13 @@
         <v>73</v>
       </c>
       <c r="AG148" t="s" s="2">
-        <v>77</v>
+        <v>445</v>
       </c>
       <c r="AH148" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="AI148" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AJ148" t="s" s="2">
         <v>73</v>
@@ -20787,7 +20785,7 @@
     </row>
     <row r="149">
       <c r="A149" t="s" s="2">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="B149" t="s" s="2">
         <v>446</v>
@@ -20801,10 +20799,10 @@
       </c>
       <c r="F149" s="2"/>
       <c r="G149" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="H149" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="I149" t="s" s="2">
         <v>73</v>
@@ -20816,13 +20814,13 @@
         <v>73</v>
       </c>
       <c r="L149" t="s" s="2">
-        <v>89</v>
+        <v>76</v>
       </c>
       <c r="M149" t="s" s="2">
-        <v>443</v>
+        <v>448</v>
       </c>
       <c r="N149" t="s" s="2">
-        <v>443</v>
+        <v>449</v>
       </c>
       <c r="O149" s="2"/>
       <c r="P149" s="2"/>
@@ -20873,13 +20871,13 @@
         <v>73</v>
       </c>
       <c r="AG149" t="s" s="2">
-        <v>446</v>
+        <v>77</v>
       </c>
       <c r="AH149" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AI149" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AJ149" t="s" s="2">
         <v>73</v>
@@ -20890,13 +20888,13 @@
     </row>
     <row r="150">
       <c r="A150" t="s" s="2">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="C150" t="s" s="2">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="D150" s="2"/>
       <c r="E150" t="s" s="2">
@@ -20904,10 +20902,10 @@
       </c>
       <c r="F150" s="2"/>
       <c r="G150" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="H150" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="I150" t="s" s="2">
         <v>73</v>
@@ -20919,13 +20917,13 @@
         <v>73</v>
       </c>
       <c r="L150" t="s" s="2">
-        <v>76</v>
+        <v>249</v>
       </c>
       <c r="M150" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="N150" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="O150" s="2"/>
       <c r="P150" s="2"/>
@@ -20976,13 +20974,13 @@
         <v>73</v>
       </c>
       <c r="AG150" t="s" s="2">
-        <v>77</v>
+        <v>450</v>
       </c>
       <c r="AH150" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="AI150" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AJ150" t="s" s="2">
         <v>73</v>
@@ -20993,13 +20991,13 @@
     </row>
     <row r="151">
       <c r="A151" t="s" s="2">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C151" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="D151" s="2"/>
       <c r="E151" t="s" s="2">
@@ -21022,13 +21020,13 @@
         <v>73</v>
       </c>
       <c r="L151" t="s" s="2">
-        <v>249</v>
+        <v>112</v>
       </c>
       <c r="M151" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="N151" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="O151" s="2"/>
       <c r="P151" s="2"/>
@@ -21043,7 +21041,7 @@
         <v>73</v>
       </c>
       <c r="U151" t="s" s="2">
-        <v>73</v>
+        <v>455</v>
       </c>
       <c r="V151" t="s" s="2">
         <v>73</v>
@@ -21055,13 +21053,11 @@
         <v>73</v>
       </c>
       <c r="Y151" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z151" t="s" s="2">
-        <v>73</v>
-      </c>
+        <v>456</v>
+      </c>
+      <c r="Z151" s="2"/>
       <c r="AA151" t="s" s="2">
-        <v>73</v>
+        <v>259</v>
       </c>
       <c r="AB151" t="s" s="2">
         <v>73</v>
@@ -21079,7 +21075,7 @@
         <v>73</v>
       </c>
       <c r="AG151" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AH151" t="s" s="2">
         <v>79</v>
@@ -21096,13 +21092,13 @@
     </row>
     <row r="152">
       <c r="A152" t="s" s="2">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="C152" t="s" s="2">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="D152" s="2"/>
       <c r="E152" t="s" s="2">
@@ -21125,13 +21121,13 @@
         <v>73</v>
       </c>
       <c r="L152" t="s" s="2">
-        <v>112</v>
+        <v>279</v>
       </c>
       <c r="M152" t="s" s="2">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="N152" t="s" s="2">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="O152" s="2"/>
       <c r="P152" s="2"/>
@@ -21146,7 +21142,7 @@
         <v>73</v>
       </c>
       <c r="U152" t="s" s="2">
-        <v>456</v>
+        <v>73</v>
       </c>
       <c r="V152" t="s" s="2">
         <v>73</v>
@@ -21158,29 +21154,31 @@
         <v>73</v>
       </c>
       <c r="Y152" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z152" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA152" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB152" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC152" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD152" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE152" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF152" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AG152" t="s" s="2">
         <v>457</v>
-      </c>
-      <c r="Z152" s="2"/>
-      <c r="AA152" t="s" s="2">
-        <v>260</v>
-      </c>
-      <c r="AB152" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC152" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD152" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE152" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF152" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AG152" t="s" s="2">
-        <v>453</v>
       </c>
       <c r="AH152" t="s" s="2">
         <v>79</v>
@@ -21197,13 +21195,13 @@
     </row>
     <row r="153">
       <c r="A153" t="s" s="2">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C153" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="D153" s="2"/>
       <c r="E153" t="s" s="2">
@@ -21211,7 +21209,7 @@
       </c>
       <c r="F153" s="2"/>
       <c r="G153" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="H153" t="s" s="2">
         <v>79</v>
@@ -21226,13 +21224,13 @@
         <v>73</v>
       </c>
       <c r="L153" t="s" s="2">
-        <v>280</v>
+        <v>89</v>
       </c>
       <c r="M153" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="N153" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="O153" s="2"/>
       <c r="P153" s="2"/>
@@ -21283,10 +21281,10 @@
         <v>73</v>
       </c>
       <c r="AG153" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AH153" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AI153" t="s" s="2">
         <v>79</v>
@@ -21300,13 +21298,13 @@
     </row>
     <row r="154">
       <c r="A154" t="s" s="2">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="C154" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="D154" s="2"/>
       <c r="E154" t="s" s="2">
@@ -21332,10 +21330,10 @@
         <v>89</v>
       </c>
       <c r="M154" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="N154" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="O154" s="2"/>
       <c r="P154" s="2"/>
@@ -21386,7 +21384,7 @@
         <v>73</v>
       </c>
       <c r="AG154" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="AH154" t="s" s="2">
         <v>74</v>
@@ -21403,13 +21401,13 @@
     </row>
     <row r="155">
       <c r="A155" t="s" s="2">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="C155" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="D155" s="2"/>
       <c r="E155" t="s" s="2">
@@ -21417,7 +21415,7 @@
       </c>
       <c r="F155" s="2"/>
       <c r="G155" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="H155" t="s" s="2">
         <v>79</v>
@@ -21432,13 +21430,13 @@
         <v>73</v>
       </c>
       <c r="L155" t="s" s="2">
-        <v>89</v>
+        <v>297</v>
       </c>
       <c r="M155" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="N155" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="O155" s="2"/>
       <c r="P155" s="2"/>
@@ -21489,10 +21487,10 @@
         <v>73</v>
       </c>
       <c r="AG155" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="AH155" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="AI155" t="s" s="2">
         <v>79</v>
@@ -21506,13 +21504,13 @@
     </row>
     <row r="156">
       <c r="A156" t="s" s="2">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="C156" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="D156" s="2"/>
       <c r="E156" t="s" s="2">
@@ -21535,13 +21533,13 @@
         <v>73</v>
       </c>
       <c r="L156" t="s" s="2">
-        <v>297</v>
+        <v>276</v>
       </c>
       <c r="M156" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="N156" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="O156" s="2"/>
       <c r="P156" s="2"/>
@@ -21592,7 +21590,7 @@
         <v>73</v>
       </c>
       <c r="AG156" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AH156" t="s" s="2">
         <v>79</v>
@@ -21609,13 +21607,13 @@
     </row>
     <row r="157">
       <c r="A157" t="s" s="2">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="C157" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="D157" s="2"/>
       <c r="E157" t="s" s="2">
@@ -21638,13 +21636,13 @@
         <v>73</v>
       </c>
       <c r="L157" t="s" s="2">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="M157" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="N157" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="O157" s="2"/>
       <c r="P157" s="2"/>
@@ -21695,7 +21693,7 @@
         <v>73</v>
       </c>
       <c r="AG157" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="AH157" t="s" s="2">
         <v>79</v>
@@ -21712,13 +21710,13 @@
     </row>
     <row r="158">
       <c r="A158" t="s" s="2">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C158" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="D158" s="2"/>
       <c r="E158" t="s" s="2">
@@ -21741,13 +21739,13 @@
         <v>73</v>
       </c>
       <c r="L158" t="s" s="2">
-        <v>277</v>
+        <v>193</v>
       </c>
       <c r="M158" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="N158" t="s" s="2">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="O158" s="2"/>
       <c r="P158" s="2"/>
@@ -21774,13 +21772,11 @@
         <v>73</v>
       </c>
       <c r="Y158" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z158" t="s" s="2">
-        <v>73</v>
-      </c>
+        <v>196</v>
+      </c>
+      <c r="Z158" s="2"/>
       <c r="AA158" t="s" s="2">
-        <v>73</v>
+        <v>474</v>
       </c>
       <c r="AB158" t="s" s="2">
         <v>73</v>
@@ -21798,7 +21794,7 @@
         <v>73</v>
       </c>
       <c r="AG158" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="AH158" t="s" s="2">
         <v>79</v>
@@ -21815,13 +21811,13 @@
     </row>
     <row r="159">
       <c r="A159" t="s" s="2">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="C159" t="s" s="2">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="D159" s="2"/>
       <c r="E159" t="s" s="2">
@@ -21844,13 +21840,13 @@
         <v>73</v>
       </c>
       <c r="L159" t="s" s="2">
-        <v>193</v>
+        <v>476</v>
       </c>
       <c r="M159" t="s" s="2">
-        <v>473</v>
+        <v>477</v>
       </c>
       <c r="N159" t="s" s="2">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="O159" s="2"/>
       <c r="P159" s="2"/>
@@ -21877,29 +21873,31 @@
         <v>73</v>
       </c>
       <c r="Y159" t="s" s="2">
-        <v>196</v>
-      </c>
-      <c r="Z159" s="2"/>
+        <v>73</v>
+      </c>
+      <c r="Z159" t="s" s="2">
+        <v>73</v>
+      </c>
       <c r="AA159" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB159" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC159" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD159" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE159" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF159" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AG159" t="s" s="2">
         <v>475</v>
-      </c>
-      <c r="AB159" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC159" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD159" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE159" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF159" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AG159" t="s" s="2">
-        <v>472</v>
       </c>
       <c r="AH159" t="s" s="2">
         <v>79</v>
@@ -21916,13 +21914,13 @@
     </row>
     <row r="160">
       <c r="A160" t="s" s="2">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="C160" t="s" s="2">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="D160" s="2"/>
       <c r="E160" t="s" s="2">
@@ -21930,7 +21928,7 @@
       </c>
       <c r="F160" s="2"/>
       <c r="G160" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="H160" t="s" s="2">
         <v>79</v>
@@ -21945,13 +21943,13 @@
         <v>73</v>
       </c>
       <c r="L160" t="s" s="2">
-        <v>477</v>
+        <v>276</v>
       </c>
       <c r="M160" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="N160" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="O160" s="2"/>
       <c r="P160" s="2"/>
@@ -22002,10 +22000,10 @@
         <v>73</v>
       </c>
       <c r="AG160" t="s" s="2">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="AH160" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AI160" t="s" s="2">
         <v>79</v>
@@ -22019,13 +22017,13 @@
     </row>
     <row r="161">
       <c r="A161" t="s" s="2">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="C161" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="D161" s="2"/>
       <c r="E161" t="s" s="2">
@@ -22036,7 +22034,7 @@
         <v>74</v>
       </c>
       <c r="H161" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="I161" t="s" s="2">
         <v>73</v>
@@ -22048,13 +22046,13 @@
         <v>73</v>
       </c>
       <c r="L161" t="s" s="2">
-        <v>277</v>
+        <v>89</v>
       </c>
       <c r="M161" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="N161" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="O161" s="2"/>
       <c r="P161" s="2"/>
@@ -22105,13 +22103,13 @@
         <v>73</v>
       </c>
       <c r="AG161" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="AH161" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI161" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AJ161" t="s" s="2">
         <v>73</v>
@@ -22122,13 +22120,13 @@
     </row>
     <row r="162">
       <c r="A162" t="s" s="2">
-        <v>447</v>
+        <v>482</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="C162" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="D162" s="2"/>
       <c r="E162" t="s" s="2">
@@ -22151,13 +22149,13 @@
         <v>73</v>
       </c>
       <c r="L162" t="s" s="2">
-        <v>89</v>
+        <v>76</v>
       </c>
       <c r="M162" t="s" s="2">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="N162" t="s" s="2">
-        <v>482</v>
+        <v>486</v>
       </c>
       <c r="O162" s="2"/>
       <c r="P162" s="2"/>
@@ -22208,7 +22206,7 @@
         <v>73</v>
       </c>
       <c r="AG162" t="s" s="2">
-        <v>481</v>
+        <v>77</v>
       </c>
       <c r="AH162" t="s" s="2">
         <v>74</v>
@@ -22225,13 +22223,13 @@
     </row>
     <row r="163">
       <c r="A163" t="s" s="2">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="C163" t="s" s="2">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="D163" s="2"/>
       <c r="E163" t="s" s="2">
@@ -22239,10 +22237,10 @@
       </c>
       <c r="F163" s="2"/>
       <c r="G163" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="H163" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="I163" t="s" s="2">
         <v>73</v>
@@ -22254,13 +22252,13 @@
         <v>73</v>
       </c>
       <c r="L163" t="s" s="2">
-        <v>76</v>
+        <v>488</v>
       </c>
       <c r="M163" t="s" s="2">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="N163" t="s" s="2">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="O163" s="2"/>
       <c r="P163" s="2"/>
@@ -22311,13 +22309,13 @@
         <v>73</v>
       </c>
       <c r="AG163" t="s" s="2">
-        <v>77</v>
+        <v>487</v>
       </c>
       <c r="AH163" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="AI163" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AJ163" t="s" s="2">
         <v>73</v>
@@ -22328,13 +22326,13 @@
     </row>
     <row r="164">
       <c r="A164" t="s" s="2">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="C164" t="s" s="2">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="D164" s="2"/>
       <c r="E164" t="s" s="2">
@@ -22345,7 +22343,7 @@
         <v>79</v>
       </c>
       <c r="H164" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="I164" t="s" s="2">
         <v>73</v>
@@ -22357,13 +22355,13 @@
         <v>73</v>
       </c>
       <c r="L164" t="s" s="2">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="M164" t="s" s="2">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="N164" t="s" s="2">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="O164" s="2"/>
       <c r="P164" s="2"/>
@@ -22414,13 +22412,13 @@
         <v>73</v>
       </c>
       <c r="AG164" t="s" s="2">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="AH164" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AI164" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AJ164" t="s" s="2">
         <v>73</v>
@@ -22431,13 +22429,13 @@
     </row>
     <row r="165">
       <c r="A165" t="s" s="2">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="C165" t="s" s="2">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="D165" s="2"/>
       <c r="E165" t="s" s="2">
@@ -22460,13 +22458,13 @@
         <v>73</v>
       </c>
       <c r="L165" t="s" s="2">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="M165" t="s" s="2">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="N165" t="s" s="2">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="O165" s="2"/>
       <c r="P165" s="2"/>
@@ -22517,7 +22515,7 @@
         <v>73</v>
       </c>
       <c r="AG165" t="s" s="2">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="AH165" t="s" s="2">
         <v>79</v>
@@ -22534,13 +22532,13 @@
     </row>
     <row r="166">
       <c r="A166" t="s" s="2">
-        <v>483</v>
+        <v>496</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="C166" t="s" s="2">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="D166" s="2"/>
       <c r="E166" t="s" s="2">
@@ -22548,7 +22546,7 @@
       </c>
       <c r="F166" s="2"/>
       <c r="G166" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="H166" t="s" s="2">
         <v>75</v>
@@ -22563,13 +22561,13 @@
         <v>73</v>
       </c>
       <c r="L166" t="s" s="2">
-        <v>495</v>
+        <v>76</v>
       </c>
       <c r="M166" t="s" s="2">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="N166" t="s" s="2">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="O166" s="2"/>
       <c r="P166" s="2"/>
@@ -22620,10 +22618,10 @@
         <v>73</v>
       </c>
       <c r="AG166" t="s" s="2">
-        <v>494</v>
+        <v>77</v>
       </c>
       <c r="AH166" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AI166" t="s" s="2">
         <v>75</v>
@@ -22637,13 +22635,13 @@
     </row>
     <row r="167">
       <c r="A167" t="s" s="2">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>497</v>
+        <v>501</v>
       </c>
       <c r="C167" t="s" s="2">
-        <v>497</v>
+        <v>501</v>
       </c>
       <c r="D167" s="2"/>
       <c r="E167" t="s" s="2">
@@ -22651,10 +22649,10 @@
       </c>
       <c r="F167" s="2"/>
       <c r="G167" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="H167" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="I167" t="s" s="2">
         <v>73</v>
@@ -22666,13 +22664,13 @@
         <v>73</v>
       </c>
       <c r="L167" t="s" s="2">
-        <v>76</v>
+        <v>112</v>
       </c>
       <c r="M167" t="s" s="2">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="N167" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="O167" s="2"/>
       <c r="P167" s="2"/>
@@ -22699,13 +22697,11 @@
         <v>73</v>
       </c>
       <c r="Y167" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z167" t="s" s="2">
-        <v>73</v>
-      </c>
+        <v>456</v>
+      </c>
+      <c r="Z167" s="2"/>
       <c r="AA167" t="s" s="2">
-        <v>73</v>
+        <v>503</v>
       </c>
       <c r="AB167" t="s" s="2">
         <v>73</v>
@@ -22723,13 +22719,13 @@
         <v>73</v>
       </c>
       <c r="AG167" t="s" s="2">
-        <v>77</v>
+        <v>501</v>
       </c>
       <c r="AH167" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="AI167" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AJ167" t="s" s="2">
         <v>73</v>
@@ -22740,13 +22736,13 @@
     </row>
     <row r="168">
       <c r="A168" t="s" s="2">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="C168" t="s" s="2">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="D168" s="2"/>
       <c r="E168" t="s" s="2">
@@ -22769,13 +22765,13 @@
         <v>73</v>
       </c>
       <c r="L168" t="s" s="2">
-        <v>112</v>
+        <v>249</v>
       </c>
       <c r="M168" t="s" s="2">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="N168" t="s" s="2">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="O168" s="2"/>
       <c r="P168" s="2"/>
@@ -22802,29 +22798,31 @@
         <v>73</v>
       </c>
       <c r="Y168" t="s" s="2">
-        <v>457</v>
-      </c>
-      <c r="Z168" s="2"/>
+        <v>73</v>
+      </c>
+      <c r="Z168" t="s" s="2">
+        <v>73</v>
+      </c>
       <c r="AA168" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB168" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC168" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD168" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE168" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF168" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AG168" t="s" s="2">
         <v>504</v>
-      </c>
-      <c r="AB168" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC168" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD168" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE168" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF168" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AG168" t="s" s="2">
-        <v>502</v>
       </c>
       <c r="AH168" t="s" s="2">
         <v>79</v>
@@ -22841,13 +22839,13 @@
     </row>
     <row r="169">
       <c r="A169" t="s" s="2">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="C169" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="D169" s="2"/>
       <c r="E169" t="s" s="2">
@@ -22873,10 +22871,10 @@
         <v>249</v>
       </c>
       <c r="M169" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="N169" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="O169" s="2"/>
       <c r="P169" s="2"/>
@@ -22927,7 +22925,7 @@
         <v>73</v>
       </c>
       <c r="AG169" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="AH169" t="s" s="2">
         <v>79</v>
@@ -22939,109 +22937,6 @@
         <v>73</v>
       </c>
       <c r="AK169" t="s" s="2">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" t="s" s="2">
-        <v>497</v>
-      </c>
-      <c r="B170" t="s" s="2">
-        <v>507</v>
-      </c>
-      <c r="C170" t="s" s="2">
-        <v>507</v>
-      </c>
-      <c r="D170" s="2"/>
-      <c r="E170" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="F170" s="2"/>
-      <c r="G170" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H170" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I170" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J170" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K170" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="L170" t="s" s="2">
-        <v>249</v>
-      </c>
-      <c r="M170" t="s" s="2">
-        <v>508</v>
-      </c>
-      <c r="N170" t="s" s="2">
-        <v>508</v>
-      </c>
-      <c r="O170" s="2"/>
-      <c r="P170" s="2"/>
-      <c r="Q170" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="R170" s="2"/>
-      <c r="S170" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T170" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U170" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V170" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W170" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X170" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y170" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z170" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA170" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB170" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC170" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD170" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE170" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF170" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AG170" t="s" s="2">
-        <v>507</v>
-      </c>
-      <c r="AH170" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI170" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ170" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AK170" t="s" s="2">
         <v>73</v>
       </c>
     </row>
